--- a/EddiewareOpeningRangeSetup/EddiewareOpeningRangeSetup/metric_results_noLookAhead_output.xlsx
+++ b/EddiewareOpeningRangeSetup/EddiewareOpeningRangeSetup/metric_results_noLookAhead_output.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_99_\Desktop\codding\OpeningRangeSetup\EddiewareOpeningRangeSetup\EddiewareOpeningRangeSetup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{243AA387-48C1-4819-A07D-46FD88FDFFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0800A1EE-CAF1-46E2-8FA1-45E382FBA8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6088" uniqueCount="1403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6093" uniqueCount="1405">
   <si>
     <t>date</t>
   </si>
@@ -4237,13 +4237,19 @@
   </si>
   <si>
     <t>time_ok</t>
+  </si>
+  <si>
+    <t>NORMAL SPEE</t>
+  </si>
+  <si>
+    <t>A+ SPEED</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4251,13 +4257,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -4269,13 +4299,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Bueno" xfId="1" builtinId="26"/>
+    <cellStyle name="Incorrecto" xfId="2" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4580,6 +4616,15 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="4" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="37" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.25">
@@ -66413,467 +66458,467 @@
         <v>46</v>
       </c>
     </row>
-    <row r="534" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A534" t="s">
+    <row r="534" spans="1:39" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A534" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="B534" t="s">
+      <c r="B534" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="C534" t="s">
+      <c r="C534" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D534">
+      <c r="D534" s="1">
         <v>29282.5</v>
       </c>
-      <c r="E534">
+      <c r="E534" s="1">
         <v>29346.25</v>
       </c>
-      <c r="F534">
+      <c r="F534" s="1">
         <v>63.75</v>
       </c>
-      <c r="G534">
+      <c r="G534" s="1">
         <v>255</v>
       </c>
-      <c r="H534">
+      <c r="H534" s="1">
         <v>29305</v>
       </c>
-      <c r="I534">
+      <c r="I534" s="1">
         <v>29343.75</v>
       </c>
-      <c r="J534">
+      <c r="J534" s="1">
         <v>155</v>
       </c>
-      <c r="K534">
+      <c r="K534" s="1">
         <v>0.60784313725490191</v>
       </c>
-      <c r="L534" t="s">
+      <c r="L534" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="M534" t="s">
+      <c r="M534" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="N534">
+      <c r="N534" s="1" t="s">
+        <v>1404</v>
+      </c>
+      <c r="O534" s="1">
+        <v>145</v>
+      </c>
+      <c r="P534" s="1">
+        <v>3746</v>
+      </c>
+      <c r="Q534" s="1">
+        <v>316</v>
+      </c>
+      <c r="R534" s="1">
+        <v>29357.45</v>
+      </c>
+      <c r="S534" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T534" s="1">
         <v>29382.5</v>
       </c>
-      <c r="O534">
+      <c r="U534" s="1">
+        <v>29352.5</v>
+      </c>
+      <c r="V534" s="1">
+        <v>29412.5</v>
+      </c>
+      <c r="W534" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X534" s="1">
+        <v>175</v>
+      </c>
+      <c r="Y534" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z534" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA534" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC534" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD534" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE534" s="1">
+        <v>7</v>
+      </c>
+      <c r="AF534" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG534" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH534" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI534" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ534" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK534" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL534" s="1">
+        <v>7</v>
+      </c>
+      <c r="AM534" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="535" spans="1:39" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A535" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C535" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D535" s="1">
+        <v>29146.25</v>
+      </c>
+      <c r="E535" s="1">
+        <v>29227.5</v>
+      </c>
+      <c r="F535" s="1">
+        <v>81.25</v>
+      </c>
+      <c r="G535" s="1">
+        <v>325</v>
+      </c>
+      <c r="H535" s="1">
+        <v>29166.25</v>
+      </c>
+      <c r="I535" s="1">
+        <v>29213.75</v>
+      </c>
+      <c r="J535" s="1">
+        <v>190</v>
+      </c>
+      <c r="K535" s="1">
+        <v>0.58461538461538465</v>
+      </c>
+      <c r="L535" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M535" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N535" s="1" t="s">
+        <v>1404</v>
+      </c>
+      <c r="O535" s="1">
         <v>145</v>
       </c>
-      <c r="P534">
-        <v>3746</v>
-      </c>
-      <c r="Q534">
-        <v>316</v>
-      </c>
-      <c r="R534">
-        <v>29357.45</v>
-      </c>
-      <c r="S534" t="s">
+      <c r="P535" s="1">
+        <v>3296</v>
+      </c>
+      <c r="Q535" s="1">
+        <v>398</v>
+      </c>
+      <c r="R535" s="1">
+        <v>29195.17</v>
+      </c>
+      <c r="S535" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="T535" s="1">
+        <v>29263.75</v>
+      </c>
+      <c r="U535" s="1">
+        <v>29233.75</v>
+      </c>
+      <c r="V535" s="1">
+        <v>29293.75</v>
+      </c>
+      <c r="W535" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="X535" s="1">
+        <v>85</v>
+      </c>
+      <c r="Y535" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z535" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA535" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC535" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD535" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE535" s="1">
+        <v>7</v>
+      </c>
+      <c r="AF535" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG535" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH535" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI535" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ535" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK535" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL535" s="1">
+        <v>7</v>
+      </c>
+      <c r="AM535" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="536" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A536" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B536" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C536" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D536" s="2">
+        <v>29252.5</v>
+      </c>
+      <c r="E536" s="2">
+        <v>29288.75</v>
+      </c>
+      <c r="F536" s="2">
+        <v>36.25</v>
+      </c>
+      <c r="G536" s="2">
+        <v>145</v>
+      </c>
+      <c r="H536" s="2">
+        <v>29261.25</v>
+      </c>
+      <c r="I536" s="2">
+        <v>29287.5</v>
+      </c>
+      <c r="J536" s="2">
+        <v>105</v>
+      </c>
+      <c r="K536" s="2">
+        <v>0.72413793103448265</v>
+      </c>
+      <c r="L536" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M536" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N536" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="O536" s="2">
+        <v>145</v>
+      </c>
+      <c r="P536" s="2">
+        <v>2461</v>
+      </c>
+      <c r="Q536" s="2">
+        <v>-409</v>
+      </c>
+      <c r="R536" s="2">
+        <v>29243.66</v>
+      </c>
+      <c r="S536" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="T536" s="2">
+        <v>29216.25</v>
+      </c>
+      <c r="U536" s="2">
+        <v>29246.25</v>
+      </c>
+      <c r="V536" s="2">
+        <v>29186.25</v>
+      </c>
+      <c r="W536" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X536" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y536" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z536" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA536" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC536" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD536" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE536" s="2">
+        <v>6</v>
+      </c>
+      <c r="AF536" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG536" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH536" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI536" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ536" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK536" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL536" s="2">
+        <v>6</v>
+      </c>
+      <c r="AM536" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="537" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A537" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B537" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C537" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D537" s="2">
+        <v>29460</v>
+      </c>
+      <c r="E537" s="2">
+        <v>29492.5</v>
+      </c>
+      <c r="F537" s="2">
+        <v>32.5</v>
+      </c>
+      <c r="G537" s="2">
+        <v>130</v>
+      </c>
+      <c r="H537" s="2">
+        <v>29472.5</v>
+      </c>
+      <c r="I537" s="2">
+        <v>29476.25</v>
+      </c>
+      <c r="J537" s="2">
+        <v>15</v>
+      </c>
+      <c r="K537" s="2">
+        <v>0.1153846153846154</v>
+      </c>
+      <c r="L537" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="T534">
-        <v>29382.5</v>
-      </c>
-      <c r="U534">
-        <v>29352.5</v>
-      </c>
-      <c r="V534">
-        <v>29412.5</v>
-      </c>
-      <c r="W534" t="s">
+      <c r="M537" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N537" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="O537" s="2">
+        <v>30</v>
+      </c>
+      <c r="P537" s="2">
+        <v>3078</v>
+      </c>
+      <c r="Q537" s="2">
+        <v>-22</v>
+      </c>
+      <c r="R537" s="2">
+        <v>29482.22</v>
+      </c>
+      <c r="S537" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T537" s="2">
+        <v>29500</v>
+      </c>
+      <c r="U537" s="2">
+        <v>29470</v>
+      </c>
+      <c r="V537" s="2">
+        <v>29530</v>
+      </c>
+      <c r="W537" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="X534">
-        <v>175</v>
-      </c>
-      <c r="Y534" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z534" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA534" t="s">
+      <c r="X537" s="2">
+        <v>125</v>
+      </c>
+      <c r="Y537" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z537" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA537" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AC534" t="s">
+      <c r="AC537" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AD534" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE534">
-        <v>7</v>
-      </c>
-      <c r="AF534" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG534" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH534" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI534" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ534" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK534" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL534">
-        <v>7</v>
-      </c>
-      <c r="AM534" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="535" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A535" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C535" t="s">
-        <v>41</v>
-      </c>
-      <c r="D535">
-        <v>29146.25</v>
-      </c>
-      <c r="E535">
-        <v>29227.5</v>
-      </c>
-      <c r="F535">
-        <v>81.25</v>
-      </c>
-      <c r="G535">
-        <v>325</v>
-      </c>
-      <c r="H535">
-        <v>29166.25</v>
-      </c>
-      <c r="I535">
-        <v>29213.75</v>
-      </c>
-      <c r="J535">
-        <v>190</v>
-      </c>
-      <c r="K535">
-        <v>0.58461538461538465</v>
-      </c>
-      <c r="L535" t="s">
-        <v>76</v>
-      </c>
-      <c r="M535" t="s">
-        <v>58</v>
-      </c>
-      <c r="N535">
-        <v>29263.75</v>
-      </c>
-      <c r="O535">
-        <v>145</v>
-      </c>
-      <c r="P535">
-        <v>3296</v>
-      </c>
-      <c r="Q535">
-        <v>398</v>
-      </c>
-      <c r="R535">
-        <v>29195.17</v>
-      </c>
-      <c r="S535" t="s">
-        <v>76</v>
-      </c>
-      <c r="T535">
-        <v>29263.75</v>
-      </c>
-      <c r="U535">
-        <v>29233.75</v>
-      </c>
-      <c r="V535">
-        <v>29293.75</v>
-      </c>
-      <c r="W535" t="s">
-        <v>81</v>
-      </c>
-      <c r="X535">
-        <v>85</v>
-      </c>
-      <c r="Y535" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z535" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA535" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC535" t="s">
-        <v>76</v>
-      </c>
-      <c r="AD535" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE535">
-        <v>7</v>
-      </c>
-      <c r="AF535" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG535" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH535" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI535" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ535" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK535" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL535">
-        <v>7</v>
-      </c>
-      <c r="AM535" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="536" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A536" t="s">
-        <v>1160</v>
-      </c>
-      <c r="B536" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C536" t="s">
-        <v>41</v>
-      </c>
-      <c r="D536">
-        <v>29252.5</v>
-      </c>
-      <c r="E536">
-        <v>29288.75</v>
-      </c>
-      <c r="F536">
-        <v>36.25</v>
-      </c>
-      <c r="G536">
-        <v>145</v>
-      </c>
-      <c r="H536">
-        <v>29261.25</v>
-      </c>
-      <c r="I536">
-        <v>29287.5</v>
-      </c>
-      <c r="J536">
-        <v>105</v>
-      </c>
-      <c r="K536">
-        <v>0.72413793103448265</v>
-      </c>
-      <c r="L536" t="s">
-        <v>63</v>
-      </c>
-      <c r="M536" t="s">
-        <v>43</v>
-      </c>
-      <c r="N536">
-        <v>29216.25</v>
-      </c>
-      <c r="O536">
-        <v>145</v>
-      </c>
-      <c r="P536">
-        <v>2461</v>
-      </c>
-      <c r="Q536">
-        <v>-409</v>
-      </c>
-      <c r="R536">
-        <v>29243.66</v>
-      </c>
-      <c r="S536" t="s">
-        <v>63</v>
-      </c>
-      <c r="T536">
-        <v>29216.25</v>
-      </c>
-      <c r="U536">
-        <v>29246.25</v>
-      </c>
-      <c r="V536">
-        <v>29186.25</v>
-      </c>
-      <c r="W536" t="s">
-        <v>49</v>
-      </c>
-      <c r="X536">
-        <v>75</v>
-      </c>
-      <c r="Y536" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z536" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA536" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC536" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD536" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE536">
-        <v>6</v>
-      </c>
-      <c r="AF536" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG536" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH536" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI536" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ536" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK536" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL536">
-        <v>6</v>
-      </c>
-      <c r="AM536" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="537" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A537" t="s">
-        <v>1162</v>
-      </c>
-      <c r="B537" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C537" t="s">
-        <v>41</v>
-      </c>
-      <c r="D537">
-        <v>29460</v>
-      </c>
-      <c r="E537">
-        <v>29492.5</v>
-      </c>
-      <c r="F537">
-        <v>32.5</v>
-      </c>
-      <c r="G537">
-        <v>130</v>
-      </c>
-      <c r="H537">
-        <v>29472.5</v>
-      </c>
-      <c r="I537">
-        <v>29476.25</v>
-      </c>
-      <c r="J537">
-        <v>15</v>
-      </c>
-      <c r="K537">
-        <v>0.1153846153846154</v>
-      </c>
-      <c r="L537" t="s">
-        <v>72</v>
-      </c>
-      <c r="M537" t="s">
-        <v>58</v>
-      </c>
-      <c r="N537">
-        <v>29500</v>
-      </c>
-      <c r="O537">
-        <v>30</v>
-      </c>
-      <c r="P537">
-        <v>3078</v>
-      </c>
-      <c r="Q537">
-        <v>-22</v>
-      </c>
-      <c r="R537">
-        <v>29482.22</v>
-      </c>
-      <c r="S537" t="s">
-        <v>72</v>
-      </c>
-      <c r="T537">
-        <v>29500</v>
-      </c>
-      <c r="U537">
-        <v>29470</v>
-      </c>
-      <c r="V537">
-        <v>29530</v>
-      </c>
-      <c r="W537" t="s">
-        <v>42</v>
-      </c>
-      <c r="X537">
-        <v>125</v>
-      </c>
-      <c r="Y537" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z537" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA537" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC537" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD537" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE537">
+      <c r="AD537" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE537" s="2">
         <v>5</v>
       </c>
-      <c r="AF537" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG537" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH537" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI537" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ537" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK537" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL537">
+      <c r="AF537" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG537" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH537" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI537" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ537" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK537" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL537" s="2">
         <v>5</v>
       </c>
-      <c r="AM537" t="s">
+      <c r="AM537" s="2" t="s">
         <v>46</v>
       </c>
     </row>
@@ -66917,8 +66962,8 @@
       <c r="M538" t="s">
         <v>43</v>
       </c>
-      <c r="N538">
-        <v>29212.5</v>
+      <c r="N538" s="2" t="s">
+        <v>1403</v>
       </c>
       <c r="O538">
         <v>115</v>
